--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
@@ -95,7 +95,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -154,27 +154,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>8.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t/>
+          <t>25.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -189,24 +189,24 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t/>
+          <t>-99.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t/>
+          <t>25.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -236,44 +236,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>7885.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -295,27 +295,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4981.86</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t/>
+          <t>22.03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -330,19 +330,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 01-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -352,22 +352,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -377,7 +377,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -389,32 +389,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6556.53</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t/>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -424,19 +424,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -446,22 +446,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4789.23</t>
+          <t>13665.11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -471,44 +471,44 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5689.02</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>417779.74</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -518,19 +518,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -540,22 +540,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5869.18</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>31.08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>19.08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -565,19 +565,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5869.18</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>24.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -612,44 +612,44 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 05-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5515.16</t>
+          <t>148.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t/>
+          <t>21.10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>30.09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -659,19 +659,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -681,22 +681,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>29.10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t/>
+          <t>26.10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -706,39 +706,39 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6364.90</t>
+          <t>15648.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -753,19 +753,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -775,22 +775,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.12</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10020.50</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -800,19 +800,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5236.01</t>
+          <t/>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5236.01</t>
+          <t/>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -847,39 +847,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5692.86</t>
+          <t/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.60</t>
+          <t/>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1198,22 +1198,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>24.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>5.20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1223,19 +1223,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Mahnung Finanzamt.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>127.30</t>
+          <t>2052.97</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t/>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,22 +1292,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1329,32 +1329,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>17.02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41467 - Accountings 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1517,12 +1517,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1564,12 +1564,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1579,17 +1579,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml::41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::Accountings 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1658,12 +1658,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 05-2024.eml::Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::Accountings 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1799,12 +1799,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1814,17 +1814,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::Accountings 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1893,12 +1893,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1908,17 +1908,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::Accountings 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t/>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t/>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>127.30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::Accountings 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2081,32 +2081,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t/>
+          <t>Stadt Chemnitz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2128,32 +2128,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Stadt Chemnitz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::Accountings 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2222,12 +2222,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>820.20</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::Accountings 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::Accountings 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2410,7 +2410,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>820.20</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39922 - Accountings 11-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2598,12 +2598,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings122023.zip::40578 - Accountings 12-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t/>
+          <t>1.77</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2680,12 +2680,153 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrebestellung465795beiwebergmbh.zip::agb_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>11062.00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
@@ -75,12 +75,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t/>
+          <t>249.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t/>
+          <t>2496.77</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -95,19 +95,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1 (2)-1.pdf</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -122,12 +122,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>702400.72</t>
+          <t>941.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>516.00</t>
+          <t>2419.35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -142,7 +142,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1.pdf</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -154,27 +154,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>682.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_02-2024_DivAuswertungen_00006_5Z1.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -201,27 +201,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-99.00</t>
+          <t>2413.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -236,7 +236,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -248,32 +248,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7885.99</t>
+          <t>2413.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1__copy2.pdf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -295,27 +295,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>366.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -330,7 +330,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -342,27 +342,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>416.13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -377,7 +377,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_05-2024_DivAuswertungen_DivMitarbeiter_EZ1.pdf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -389,32 +389,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>1118.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1806.00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06-2024_DivAuswertungen_DivMitarbeiter_HZ1.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -436,32 +436,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13665.11</t>
+          <t/>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>946.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-30.30</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06_2025_Div_Auswertungen_Div_Mitarbeiter.pdf</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -483,32 +483,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>1248.39</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>1914.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_07-2024_DivAuswertungen_DivMitarbeiter_KZ1.pdf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -530,32 +530,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t/>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>1664.52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00074_NZ1.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -577,27 +577,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t/>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t/>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -612,44 +612,44 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00098_NZ1.pdf</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>148.00</t>
+          <t/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t/>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -659,44 +659,44 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.10</t>
+          <t>702400.72</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>516.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -718,27 +718,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15648.95</t>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>2236.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_DivAuswertungen_DivMitarbeiter_QZ1.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -765,32 +765,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t/>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>2619.35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_Brutto_NettoProbe_00025_ZZ1.pdf</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>2653.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>11.01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_DivAuswertungen_DivMitarbeiter_ZZ1.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -864,22 +864,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>2196.75</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -894,39 +894,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_April_2025.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>10.06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -941,39 +941,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t>1798.00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07.2025</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025__copy2.pdf</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juni_2025.pdf</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1047,27 +1047,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>6239.86</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1077,24 +1077,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t/>
+          <t>27.12.2023</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Pay Roll 12.2023.pdf</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>84.00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Seizures.pdf</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>1215.78</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1176,19 +1176,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Zoll Kitanov.pdf</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5889.13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t/>
+          <t>29.01.2024</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>5692.86</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t/>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2025.pdf</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,32 +1292,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7277.62</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t/>
+          <t>27.02.2024</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2024.pdf</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1339,32 +1339,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4981.86</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t/>
+          <t>26.02.2025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2025.pdf</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1376,7 +1376,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1386,32 +1386,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6556.53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t/>
+          <t>26.03.2024</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2024.pdf</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1423,42 +1423,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>27.03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>4789.23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t/>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2025.pdf</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1480,32 +1480,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5689.02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t/>
+          <t>26.04.2024</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4518.02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t/>
+          <t>28.04.2025</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1574,32 +1574,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5869.18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t/>
+          <t>29.05.2024</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2024.pdf</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1621,32 +1621,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4634.82</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t/>
+          <t>27.05.2025</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5991.28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t/>
+          <t>26.06.2024</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2024.pdf</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1705,7 +1705,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1715,32 +1715,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>26.06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2474.01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t/>
+          <t>26.06.2025</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1762,32 +1762,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>29.07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5515.16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t/>
+          <t>29.07.2024</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 07-2024.pdf</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1809,32 +1809,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7002.40</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t/>
+          <t>28.08.2024</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 08-2024.pdf</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1856,32 +1856,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7304.67</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t/>
+          <t>26.09.2024</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 09-2024.pdf</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1903,32 +1903,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6364.90</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t/>
+          <t>28.10.2024</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 10-2024.pdf</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>27.11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7150.71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t/>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 11-2024.pdf</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -1987,27 +1987,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>23.12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t/>
+          <t>5236.01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2017,44 +2017,44 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t/>
+          <t>23.12.2024</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 12-2024.pdf</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>127.30</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2081,12 +2081,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>-99.00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2128,12 +2128,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2143,17 +2143,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>7885.99</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2175,32 +2175,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2222,32 +2222,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>820.20</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2269,32 +2269,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2316,32 +2316,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>13665.11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2363,32 +2363,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2410,32 +2410,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2457,32 +2457,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2504,32 +2504,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>148.00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2551,32 +2551,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>29.10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2598,32 +2598,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>15648.95</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2645,32 +2645,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>25.10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2702,22 +2702,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t/>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t/>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2727,44 +2727,44 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t/>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t/>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t/>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2774,57 +2774,2924 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Arbeitsbescheinigung Georgi Stefanov.pdf</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>13649.05</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>13649.05</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>41544.44</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>41544.44</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gewerbesteuer</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>24.02</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2494.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2052.97</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>Umsatzsteuer</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>12.46</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>12.42</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>17.02</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>13.04</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>19.00</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>12.44</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>11.03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>14.03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>13.36</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10.04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>12.48</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>12.52</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>11.07</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>12.54</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10.08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>7.09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>19.11</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>14.03</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>14.03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>127.30</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>11.08</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Lohnsteuer</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>366.67</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1548.00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Stadt Chemnitz</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>17.03</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Stadt Chemnitz</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>12.05</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-25.00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Gewerbesteuer</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>29.03</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>16.01</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-213.26</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>29.03.2023</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>68848.69</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>56169.51</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12.01</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>54426.97</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>52656.37</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>13.09</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1250.78</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1222.78</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Stadt Chemnitz</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>56666.80</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>15.02</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>57567.96</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>53690.09</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>12.04</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>54751.98</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>51557.87</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>47793.00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9.08</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1568.99</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4654.34</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4809.45</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hauptzollamt</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2352.89</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>18.07</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3752.34</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>other public liability</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2312.56</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>10499.90</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>820.20</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>11062.00</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
@@ -56,11 +56,26 @@
           <t>confidence</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>source_snippet</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>matched_pattern</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -101,13 +116,28 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 249,68</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -148,13 +178,28 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 941,48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -174,7 +219,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>408.19</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -195,13 +240,28 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 682,88</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t/>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -221,7 +281,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -242,13 +302,28 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.413,55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -268,7 +343,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -289,13 +364,28 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.413,55</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t/>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -336,13 +426,28 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 366,67</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -362,7 +467,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -383,13 +488,28 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 416,13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -430,13 +550,28 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 1.118,00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -477,13 +612,28 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub2000 Gehalt L L J 946,00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -524,13 +674,28 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 1.248,39</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -571,13 +736,28 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 1.664,52</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,13 +798,28 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -665,13 +860,28 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -686,7 +896,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>702400.72</t>
+          <t/>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -712,13 +922,28 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 516,00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,13 +984,28 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.494,00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t/>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -806,13 +1046,28 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub 2000 Gehalt L L J 2.619,35</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t/>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -832,7 +1087,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -853,13 +1108,28 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.653,25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -874,7 +1144,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2196.75</t>
+          <t/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -900,13 +1170,28 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bezahlter Urlaub2000 Gehalt L L J 2.494,00</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -921,12 +1206,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t/>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -946,14 +1231,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -968,7 +1268,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t/>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -994,13 +1294,28 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. ***Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 07/2025 1.798,00</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1041,6 +1356,21 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1392,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>2653.25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1088,6 +1418,21 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.653,25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1454,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>27.08</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t/>
@@ -1135,6 +1480,21 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 1 84,00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1516,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>1215.78</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t/>
@@ -1182,6 +1542,21 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 1 215,78</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1578,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>249.68</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1229,13 +1604,28 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 249,68</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,7 +1640,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>83.23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1276,6 +1666,21 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 83,23</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1702,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>682.88</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,13 +1728,28 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 682,88</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1344,7 +1764,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t/>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1370,6 +1790,21 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. *** Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 02/2025 4.981,86</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1826,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>2413.55</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1417,13 +1852,28 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.413,55</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1438,7 +1888,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t/>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1464,6 +1914,21 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. *** Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 03/2025 4.789,23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1950,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>344.00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1511,13 +1976,28 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 344,00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1532,7 +2012,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t/>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1558,6 +2038,21 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. ***Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 04/2025 4.518,02</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1579,7 +2074,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>416.13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1605,13 +2100,28 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 416,13</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1626,7 +2136,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t/>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1652,6 +2162,21 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. ***Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 05/2025 4.634,82</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1673,7 +2198,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>1118.00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1699,13 +2224,28 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 1.118,00</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1720,7 +2260,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t/>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1746,6 +2286,21 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bezahlt wurden. ***Finanzamt 09097 Chemnitz Bar/Einzug 215/291/01497 06/2025 2.474,01</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>bezahlt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1767,7 +2322,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>1248.39</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1793,6 +2348,21 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 1.248,39</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1814,7 +2384,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>2496.77</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1840,13 +2410,28 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.496,77</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1861,7 +2446,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1887,6 +2472,21 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 2.494,00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1908,7 +2508,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>1241.94</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1934,6 +2534,21 @@
       <c r="I41" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 1.241,94</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2570,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>183.33</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1981,13 +2596,28 @@
       <c r="I42" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 183,33</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2002,7 +2632,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>354.84</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2028,18 +2658,33 @@
       <c r="I43" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 354,84</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2049,12 +2694,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t/>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2069,19 +2714,34 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>zahlung Referenz VZ2203040640020203 Mandat 025823 Einreicher-ID DE37SCC00000040819 SHELL KALOTINA//KALOTINA/BG 2022-03-02T06:45:16 Folgenr. 001 Verfalld. 2312 Entgelt 0,03 EUR</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2096,17 +2756,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-99.00</t>
+          <t/>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>-200.00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>1.23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2116,19 +2776,34 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>zahlung 02/2023 -200,00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2143,17 +2818,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7885.99</t>
+          <t/>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>-300.00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2163,44 +2838,59 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>zahlung 04/2022 -300,00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t/>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>-433.08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2210,19 +2900,34 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>zahlung KBS 83141249 KRT0001/12.23</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2237,17 +2942,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t/>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-41.50</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>-30.30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2257,19 +2962,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>zahlung Referenz VZ2207050126450407 Mandat 020468 Einreicher-ID DE37SCC00000040819 LOUNGE 130//CHEMNITZ/DE 2022-07-04T00:34:54 Folgenr. 001 Verfalld. 2312 -41,50</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2284,12 +3004,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t/>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2304,12 +3024,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>zahlung KBS 83141246 KRT0001/12.23</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
@@ -2331,17 +3066,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13665.11</t>
+          <t/>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>-300.00</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-30.30</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2351,19 +3086,34 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>zahlung 08/2022 -300,00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2373,22 +3123,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t/>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2398,19 +3148,34 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>zahlung v om 12.07</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2425,17 +3190,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t/>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>-1200.00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2445,19 +3210,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>zahlung) 10 /2022 -1.200,00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2472,17 +3252,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t/>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>-700.00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t/>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2492,19 +3272,34 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>zahlung 10/2021 -700,00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2519,17 +3314,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>148.00</t>
+          <t/>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21.10</t>
+          <t>-1300.00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t/>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2539,19 +3334,34 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>zahlung 12/2021 -1.300,00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2566,17 +3376,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29.10</t>
+          <t/>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.10</t>
+          <t>-200.00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2586,39 +3396,54 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>zahlung) 11 /2022 -200,00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t/>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15648.95</t>
+          <t/>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>915.48</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2633,24 +3458,39 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>zahlung 2000 Gehalt L L J 915,48</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2660,17 +3500,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>25.10</t>
+          <t/>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t/>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t/>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2680,19 +3520,34 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2727,19 +3582,34 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Arbeitsbescheinigung Georgi Stefanov.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2774,44 +3644,59 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>23263.84</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t/>
+          <t>5.20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2821,29 +3706,44 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Arbeitsbescheinigung Georgi Stefanov.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>FORDERUNG 23.263,84</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Forderung</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t/>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2868,29 +3768,44 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 02.04.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2900,12 +3815,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t>30281.89</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2915,29 +3830,44 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 30.281,89</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2947,12 +3877,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t/>
+          <t>25150.59</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2962,29 +3892,44 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025(1).docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 25.150,59</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2994,12 +3939,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t/>
+          <t>18516.48</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3009,44 +3954,59 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 18.516,48</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13649.05</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3056,44 +4016,59 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t/>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>41544.44</t>
+          <t>20797.47</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3103,19 +4078,34 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 20.797,47</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3125,22 +4115,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t/>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>24159.32</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3150,44 +4140,59 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 24.159,32</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2052.97</t>
+          <t/>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t/>
+          <t>22523.36</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3197,19 +4202,34 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 22.523,36</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3224,19 +4244,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t/>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>22853.99</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>10.01</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t/>
@@ -3244,19 +4264,34 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/39922 - Accountings 11-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 22.853,99</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3271,19 +4306,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t/>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
+          <t>24018.01</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t/>
@@ -3291,19 +4326,34 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/40578 - Accountings 12-2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 24.018,01</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3318,19 +4368,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t/>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>23553.36</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>13.04</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t/>
@@ -3338,24 +4388,39 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 23.553,36</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t/>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3365,17 +4430,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t/>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>23067.09</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3385,19 +4450,34 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 23.067,09</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3412,19 +4492,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t/>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>22536.76</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t/>
@@ -3432,19 +4512,34 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 22.536,76</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3459,19 +4554,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t/>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>24226.58</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t/>
@@ -3479,19 +4574,34 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 01-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 24.226,58</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3506,19 +4616,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t/>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>27948.98</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>10.04</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t/>
@@ -3526,19 +4636,34 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 27.948,98</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3553,19 +4678,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t/>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>23984.73</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t/>
@@ -3573,24 +4698,39 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>zahlung / Überschuss 23.984,73</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t/>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3600,17 +4740,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t/>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t/>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3620,24 +4760,39 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3647,17 +4802,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>797.30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t/>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3667,44 +4822,59 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 06-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag 797,30</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Lohnsteuer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>366.67</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t/>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3714,44 +4884,59 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 07-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag pro Monat 366,67</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Gesamtbetrag</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Stadt Chemnitz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t/>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t/>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3761,44 +4946,59 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 09-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>zahlung CRM 56000375 KRT0001/12.24</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Stadt Chemnitz</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t/>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3808,19 +5008,34 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 10-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>zahlung CRM 56000375 KRT0001/12.24</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3830,44 +5045,59 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t/>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t/>
+          <t>29.03.2023</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ZAHLUNG 1800 V. 14.01</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3877,22 +5107,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t/>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-13222.10</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>68848.69</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3902,29 +5132,44 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 12-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>zahlung 2023 Rainer Neumeier - Garagenvermietung; BIC: HYVEDEMM497; IBAN: DE43 8702 0086 5070 1730 79 -13.222,10</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3934,7 +5179,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t/>
+          <t>56169.51</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3949,39 +5194,54 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 29 56.169,51</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Umsatzsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>127.30</t>
+          <t/>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>54426.97</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3996,39 +5256,54 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 28 54.426,97</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t/>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lohnsteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>366.67</t>
+          <t/>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>52656.37</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4043,24 +5318,39 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 31 52.656,37</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4070,12 +5360,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t/>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>1250.78</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4090,24 +5380,39 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 1 250,78</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4117,17 +5422,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t/>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>1222.78</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t/>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4137,71 +5442,101 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 1 222,78</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Stadt Chemnitz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gewerbesteuer</t>
+          <t>other public liability</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t/>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>56666.80</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-213.26</t>
+          <t/>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>29.03.2023</t>
+          <t/>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 32 56.666,80</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4211,17 +5546,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t/>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>57567.96</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>68848.69</t>
+          <t/>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4231,19 +5566,34 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 31 57.567,96</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4258,12 +5608,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>56169.51</t>
+          <t/>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>53690.09</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4278,19 +5628,34 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 29 53.690,09</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4305,12 +5670,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>54426.97</t>
+          <t/>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>54751.98</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4325,19 +5690,34 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 29 54.751,98</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4352,12 +5732,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>52656.37</t>
+          <t/>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>51557.87</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4372,19 +5752,34 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 29 51.557,87</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4399,12 +5794,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1250.78</t>
+          <t/>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>47793.00</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4419,19 +5814,34 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 27 47.793,00</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4446,12 +5856,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1222.78</t>
+          <t/>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>1568.99</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4466,24 +5876,39 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 2 1.568,99</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Stadt Chemnitz</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4493,12 +5918,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>56666.80</t>
+          <t/>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>4654.34</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4513,24 +5938,39 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 4 654,34</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4540,12 +5980,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>57567.96</t>
+          <t/>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>4809.45</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4560,19 +6000,34 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 4 809,45</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4587,12 +6042,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>53690.09</t>
+          <t/>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>2352.89</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4607,24 +6062,39 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 2 352,89</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4634,12 +6104,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>54751.98</t>
+          <t/>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>3752.34</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4654,24 +6124,39 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 3 752,34</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4681,12 +6166,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>51557.87</t>
+          <t/>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>2312.56</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4701,44 +6186,59 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Zahlungsvorgänge: 2 312,56</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>47793.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4748,44 +6248,59 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1568.99</t>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>820.20</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4795,44 +6310,59 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>steuerbetrag - Summe Vorschuss Bruttobetrag Marco Brunettin 10.499,90 EUR</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4654.34</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4842,44 +6372,59 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4809.45</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4889,44 +6434,59 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hauptzollamt</t>
+          <t/>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2352.89</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4936,44 +6496,59 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>3752.34</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4983,44 +6558,59 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Finanzamt</t>
+          <t/>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Umsatzsteuer</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2312.56</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t/>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5030,19 +6620,34 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5062,7 +6667,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5077,19 +6682,34 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5104,12 +6724,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>820.20</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5124,19 +6744,34 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5156,7 +6791,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5171,19 +6806,34 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5203,7 +6853,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5218,19 +6868,34 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5250,7 +6915,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5265,19 +6930,34 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5292,12 +6972,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>11062.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5312,19 +6992,34 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>steuerbetrag - Summe Vorschuss Bruttobetrag Marco Brunettin 11.062,00 EUR</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5344,7 +7039,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5359,7 +7054,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5367,333 +7062,19 @@
           <t>HIGH</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>11062.00</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>steuerbetrag 19,00</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Steuerbetrag</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>tax_labeled_amounts</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/tax_timeline.xlsx
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-30.30</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-433.08</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t/>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t/>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t/>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t/>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t/>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>68848.69</t>
+          <t/>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Gewerbesteuer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Hauptzollamt</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>other public liability</t>
+          <t>Finanzamt</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
